--- a/public/templates/raid_log_intermediate_example.xlsx
+++ b/public/templates/raid_log_intermediate_example.xlsx
@@ -1,58 +1,253 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="RAID log" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="RAID log" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Instructions" state="visible" r:id="rId5"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="59">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Trigger</t>
+  </si>
+  <si>
+    <t>Impact</t>
+  </si>
+  <si>
+    <t>Likelihood</t>
+  </si>
+  <si>
+    <t>Mitigation</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Follow-up</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>R-001</t>
+  </si>
+  <si>
+    <t>Risk</t>
+  </si>
+  <si>
+    <t>Lead engineer on paternity leave for 4 weeks</t>
+  </si>
+  <si>
+    <t>Start of leave period</t>
+  </si>
+  <si>
+    <t>Schedule slip on v2 endpoint</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Backfill from contractor pool</t>
+  </si>
+  <si>
+    <t>Tech Lead</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>R-002</t>
+  </si>
+  <si>
+    <t>Vendor deprecating API in 90 days</t>
+  </si>
+  <si>
+    <t>Deprecation date</t>
+  </si>
+  <si>
+    <t>Integration breaks</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Begin v2 migration plan</t>
+  </si>
+  <si>
+    <t>Integration Architect</t>
+  </si>
+  <si>
+    <t>I-001</t>
+  </si>
+  <si>
+    <t>Issue</t>
+  </si>
+  <si>
+    <t>Scope creep: 3 new endpoints since kickoff</t>
+  </si>
+  <si>
+    <t>Sprint 2 review</t>
+  </si>
+  <si>
+    <t>Timeline slip</t>
+  </si>
+  <si>
+    <t>Re-baseline with PM</t>
+  </si>
+  <si>
+    <t>Project Coordinator</t>
+  </si>
+  <si>
+    <t>A-001</t>
+  </si>
+  <si>
+    <t>Assumption</t>
+  </si>
+  <si>
+    <t>Pilot clinic volume reflects full rollout</t>
+  </si>
+  <si>
+    <t>Go-live</t>
+  </si>
+  <si>
+    <t>Performance risk</t>
+  </si>
+  <si>
+    <t>Validate with load test</t>
+  </si>
+  <si>
+    <t>QA Lead</t>
+  </si>
+  <si>
+    <t>D-001</t>
+  </si>
+  <si>
+    <t>Dependency</t>
+  </si>
+  <si>
+    <t>Vendor sign-off on integration contract</t>
+  </si>
+  <si>
+    <t>Before expansion</t>
+  </si>
+  <si>
+    <t>Blocks Clinic 2 go-live</t>
+  </si>
+  <si>
+    <t>Escalate via vendor PM</t>
+  </si>
+  <si>
+    <t>Product Owner</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>What goes here</t>
+  </si>
+  <si>
+    <t>R-001, I-001, A-001, D-001... Use the letter prefix to make the Type obvious even in a quick scan.</t>
+  </si>
+  <si>
+    <t>One of: Risk (might happen), Issue (already happened), Assumption (taken for granted), Dependency (external blocker).</t>
+  </si>
+  <si>
+    <t>What specifically could go wrong or has gone wrong. One sentence. Use project-specific nouns — 'the vendor API', not 'the integration'.</t>
+  </si>
+  <si>
+    <t>The observable event that would move this from theoretical to real. 'Vendor announces deprecation date', 'Sprint 3 ends without sign-off', etc.</t>
+  </si>
+  <si>
+    <t>What concretely breaks or slips if this risk fires. Quantify when possible — days, dollars, SLAs.</t>
+  </si>
+  <si>
+    <t>Low / Medium / High. Keep it simple; probability maths isn't the point.</t>
+  </si>
+  <si>
+    <t>The actual action being taken — not 'monitor'. 'Backfill lead engineer from contractor pool', 'Draft v2 migration plan by Sprint 4', etc.</t>
+  </si>
+  <si>
+    <t>Named role (Tech Lead) or named person (Jordan). Never blank.</t>
+  </si>
+  <si>
+    <t>Date you'll check this item again. Every open item has one.</t>
+  </si>
+  <si>
+    <t>Open → In progress → Mitigated → Closed. A RAID log is a living artifact; update status weekly.</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0F172A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF3C7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,18 +255,72 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,216 +645,673 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J100"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="15.83203125" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
-    <col min="10" max="10" width="15.83203125" customWidth="1"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="52" customWidth="1"/>
+    <col min="4" max="4" width="32" customWidth="1"/>
+    <col min="5" max="5" width="36" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="56" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Type</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Description</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Trigger</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Impact</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Likelihood</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Mitigation</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Follow-up date</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Status</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>R-001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Risk</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Lead engineer on paternity leave for 4 weeks</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Start of leave period</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Schedule slip</v>
-      </c>
-      <c r="F2" t="str">
-        <v>High</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Backfill from contractor pool</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Tech Lead</v>
-      </c>
-      <c r="I2" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Open</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>R-002</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Risk</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Vendor deprecating API in 90 days</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Deprecation date</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Integration break</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Begin v2 migration plan</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Integration Architect</v>
-      </c>
-      <c r="I3" t="str">
-        <v>2026-06-15</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Open</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>I-001</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Issue</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Scope creep: 3 new endpoints since kickoff</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Now</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Timeline impact</v>
-      </c>
-      <c r="F4" t="str">
-        <v>High</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Re-baseline with PM</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Project Coordinator</v>
-      </c>
-      <c r="I4" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="J4" t="str">
-        <v>Open</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>A-001</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Assumption</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Pilot clinic data volume reflects full rollout</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Go-live</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Perf risk</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Validate with load test</v>
-      </c>
-      <c r="H5" t="str">
-        <v>QA Lead</v>
-      </c>
-      <c r="I5" t="str">
-        <v>2026-05-20</v>
-      </c>
-      <c r="J5" t="str">
-        <v>Open</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>D-001</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Dependency</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Vendor sign-off on integration contract</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Before expansion</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Blocker</v>
-      </c>
-      <c r="F6" t="str">
-        <v>High</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Escalate via vendor PM</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Product Owner</v>
-      </c>
-      <c r="I6" t="str">
-        <v>2026-05-05</v>
-      </c>
-      <c r="J6" t="str">
-        <v>Open</v>
-      </c>
+    <row r="1" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="5">
+        <v>46152</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="8">
+        <v>46188</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="5">
+        <v>46143</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="8">
+        <v>46162</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="5">
+        <v>46147</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" ht="36" customHeight="1" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" ht="36" customHeight="1" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" ht="36" customHeight="1" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" ht="36" customHeight="1" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" ht="36" customHeight="1" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" ht="36" customHeight="1" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" ht="36" customHeight="1" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" ht="36" customHeight="1" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" ht="36" customHeight="1" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" ht="36" customHeight="1" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" ht="36" customHeight="1" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" ht="36" customHeight="1" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" ht="36" customHeight="1" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" ht="36" customHeight="1" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I22" s="10"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I23" s="10"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I24" s="10"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I25" s="10"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I26" s="10"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I27" s="10"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I28" s="10"/>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I29" s="10"/>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I30" s="10"/>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I31" s="10"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I32" s="10"/>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I33" s="10"/>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I34" s="10"/>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I35" s="10"/>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I36" s="10"/>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I37" s="10"/>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I38" s="10"/>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I39" s="10"/>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I40" s="10"/>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I41" s="10"/>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I42" s="10"/>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I43" s="10"/>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I44" s="10"/>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I45" s="10"/>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I46" s="10"/>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I47" s="10"/>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I48" s="10"/>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I49" s="10"/>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I50" s="10"/>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I51" s="10"/>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I52" s="10"/>
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I53" s="10"/>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I54" s="10"/>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I55" s="10"/>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I56" s="10"/>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I57" s="10"/>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I58" s="10"/>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I59" s="10"/>
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I60" s="10"/>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I61" s="10"/>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I62" s="10"/>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I63" s="10"/>
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I64" s="10"/>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I65" s="10"/>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I66" s="10"/>
+    </row>
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I67" s="10"/>
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I68" s="10"/>
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I69" s="10"/>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I70" s="10"/>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I71" s="10"/>
+    </row>
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I72" s="10"/>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I73" s="10"/>
+    </row>
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I74" s="10"/>
+    </row>
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I75" s="10"/>
+    </row>
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I76" s="10"/>
+    </row>
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I77" s="10"/>
+    </row>
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I78" s="10"/>
+    </row>
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I79" s="10"/>
+    </row>
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I80" s="10"/>
+    </row>
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I81" s="10"/>
+    </row>
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I82" s="10"/>
+    </row>
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I83" s="10"/>
+    </row>
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I84" s="10"/>
+    </row>
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I85" s="10"/>
+    </row>
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I86" s="10"/>
+    </row>
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I87" s="10"/>
+    </row>
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I88" s="10"/>
+    </row>
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I89" s="10"/>
+    </row>
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I90" s="10"/>
+    </row>
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I91" s="10"/>
+    </row>
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I92" s="10"/>
+    </row>
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I93" s="10"/>
+    </row>
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I94" s="10"/>
+    </row>
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I95" s="10"/>
+    </row>
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I96" s="10"/>
+    </row>
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I97" s="10"/>
+    </row>
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I98" s="10"/>
+    </row>
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I99" s="10"/>
+    </row>
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I100" s="10"/>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
-  </ignoredErrors>
+  <autoFilter ref="A1:J1"/>
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid type" error="Choose one of: Risk, Issue, Assumption, Dependency." sqref="B10:B100">
+      <formula1>"Risk,Issue,Assumption,Dependency"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid type" error="Choose one of: Risk, Issue, Assumption, Dependency." sqref="B2:B100">
+      <formula1>"Risk,Issue,Assumption,Dependency"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F10:F100">
+      <formula1>"Low,Medium,High"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F2:F100">
+      <formula1>"Low,Medium,High"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="J10:J100">
+      <formula1>"Open,In progress,Mitigated,Closed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="J2:J100">
+      <formula1>"Open,In progress,Mitigated,Closed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageSetup orientation="landscape"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;BRAID log — intermediate example&amp;RMost fields filled; mitigations still a bit soft.</oddHeader>
+    <oddFooter>&amp;L&amp;Iproject-coordinator-launchpad</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="90" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>